--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/2.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/2.xlsx
@@ -426,13 +426,13 @@
         <v>-7.554804388912123</v>
       </c>
       <c r="E2">
-        <v>-5.405790939305961</v>
+        <v>-2.820956089623751</v>
       </c>
       <c r="F2">
-        <v>-6.289512191787202</v>
+        <v>-6.214923505736926</v>
       </c>
       <c r="G2">
-        <v>-9.229835219611797</v>
+        <v>-9.539106383890511</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.158852832089016</v>
       </c>
       <c r="E3">
-        <v>-5.650446276044359</v>
+        <v>-3.926841141614906</v>
       </c>
       <c r="F3">
-        <v>-6.591742867066005</v>
+        <v>-6.082372295777963</v>
       </c>
       <c r="G3">
-        <v>-9.460480927332819</v>
+        <v>-9.34901154848002</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.958899890061501</v>
       </c>
       <c r="E4">
-        <v>-5.940476922339615</v>
+        <v>-3.78279491190492</v>
       </c>
       <c r="F4">
-        <v>-6.231618422372947</v>
+        <v>-6.181619822674775</v>
       </c>
       <c r="G4">
-        <v>-7.99906046229479</v>
+        <v>-9.503203517517115</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.801426732835115</v>
       </c>
       <c r="E5">
-        <v>-6.261174394614814</v>
+        <v>-4.453652108349222</v>
       </c>
       <c r="F5">
-        <v>-6.302725894412958</v>
+        <v>-5.884458755901106</v>
       </c>
       <c r="G5">
-        <v>-8.9887050141679</v>
+        <v>-9.12538750784779</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.62984852778382</v>
       </c>
       <c r="E6">
-        <v>-7.519044091251402</v>
+        <v>-5.803363786335372</v>
       </c>
       <c r="F6">
-        <v>-6.216758339534127</v>
+        <v>-5.72186431697741</v>
       </c>
       <c r="G6">
-        <v>-8.964690316826028</v>
+        <v>-9.214497462128353</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.34235290314859</v>
       </c>
       <c r="E7">
-        <v>-7.869688362139326</v>
+        <v>-6.752971200321823</v>
       </c>
       <c r="F7">
-        <v>-6.2026065108247</v>
+        <v>-5.669733499584432</v>
       </c>
       <c r="G7">
-        <v>-8.57467163629895</v>
+        <v>-9.412997772663052</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.85936650337615</v>
       </c>
       <c r="E8">
-        <v>-10.03888175350152</v>
+        <v>-7.360533915560916</v>
       </c>
       <c r="F8">
-        <v>-5.912811286996724</v>
+        <v>-5.93756207662497</v>
       </c>
       <c r="G8">
-        <v>-10.02140321077923</v>
+        <v>-8.878788281173019</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.09737493656493</v>
       </c>
       <c r="E9">
-        <v>-9.621392677786373</v>
+        <v>-7.792799401963091</v>
       </c>
       <c r="F9">
-        <v>-6.33550894856245</v>
+        <v>-5.569981496939315</v>
       </c>
       <c r="G9">
-        <v>-8.717902389055517</v>
+        <v>-8.516104775163702</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.00458676114912</v>
       </c>
       <c r="E10">
-        <v>-11.14199990787399</v>
+        <v>-8.259177883065046</v>
       </c>
       <c r="F10">
-        <v>-6.002693292037485</v>
+        <v>-5.724786797174486</v>
       </c>
       <c r="G10">
-        <v>-8.29931038997899</v>
+        <v>-8.486942179508263</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.54927548771188</v>
       </c>
       <c r="E11">
-        <v>-10.89568714964878</v>
+        <v>-9.695600781350068</v>
       </c>
       <c r="F11">
-        <v>-5.541879961166745</v>
+        <v>-5.231807131685639</v>
       </c>
       <c r="G11">
-        <v>-7.987049803078314</v>
+        <v>-8.408359760042583</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.73419824583967</v>
       </c>
       <c r="E12">
-        <v>-11.08549360920628</v>
+        <v>-10.2553654534382</v>
       </c>
       <c r="F12">
-        <v>-5.545142071998969</v>
+        <v>-5.260342731977277</v>
       </c>
       <c r="G12">
-        <v>-7.179154201311191</v>
+        <v>-7.771682263021026</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.586247396909295</v>
       </c>
       <c r="E13">
-        <v>-11.84021361579863</v>
+        <v>-10.29907428456023</v>
       </c>
       <c r="F13">
-        <v>-5.355485698393217</v>
+        <v>-4.834776434095656</v>
       </c>
       <c r="G13">
-        <v>-7.498466250210515</v>
+        <v>-7.561396410366521</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.164071897941717</v>
       </c>
       <c r="E14">
-        <v>-13.72844236582892</v>
+        <v>-11.74291029479581</v>
       </c>
       <c r="F14">
-        <v>-5.349688783308426</v>
+        <v>-4.991226871992787</v>
       </c>
       <c r="G14">
-        <v>-6.970076697778519</v>
+        <v>-7.290246177972515</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.545032215300926</v>
       </c>
       <c r="E15">
-        <v>-13.16533115144912</v>
+        <v>-12.38703590917284</v>
       </c>
       <c r="F15">
-        <v>-5.352775280251257</v>
+        <v>-4.749031295864476</v>
       </c>
       <c r="G15">
-        <v>-6.784219360658295</v>
+        <v>-6.800815125446662</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.818710305081641</v>
       </c>
       <c r="E16">
-        <v>-14.05785715056888</v>
+        <v>-13.53384478077131</v>
       </c>
       <c r="F16">
-        <v>-4.939990691394832</v>
+        <v>-4.409146351924019</v>
       </c>
       <c r="G16">
-        <v>-6.75667231122602</v>
+        <v>-6.461216053482684</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.074416560543762</v>
       </c>
       <c r="E17">
-        <v>-15.36394603843915</v>
+        <v>-13.65540713703321</v>
       </c>
       <c r="F17">
-        <v>-5.026097826181036</v>
+        <v>-4.362693993077231</v>
       </c>
       <c r="G17">
-        <v>-5.651754563675486</v>
+        <v>-5.882241365210625</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.406080284154674</v>
       </c>
       <c r="E18">
-        <v>-16.45923446125235</v>
+        <v>-15.01456974027337</v>
       </c>
       <c r="F18">
-        <v>-4.406268603566694</v>
+        <v>-3.971481748124512</v>
       </c>
       <c r="G18">
-        <v>-5.391032549730184</v>
+        <v>-5.396627371691553</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.1023750059151339</v>
       </c>
       <c r="E19">
-        <v>-18.1247392741634</v>
+        <v>-15.5532588943298</v>
       </c>
       <c r="F19">
-        <v>-4.028214146440042</v>
+        <v>-3.656611014646392</v>
       </c>
       <c r="G19">
-        <v>-4.745151736109454</v>
+        <v>-5.525751889905286</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.381768024843934</v>
       </c>
       <c r="E20">
-        <v>-17.95619400007191</v>
+        <v>-16.51439127466578</v>
       </c>
       <c r="F20">
-        <v>-4.110780838946679</v>
+        <v>-3.433069444061723</v>
       </c>
       <c r="G20">
-        <v>-5.179938923964096</v>
+        <v>-5.603566262805855</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.383218844203964</v>
       </c>
       <c r="E21">
-        <v>-19.15538373051711</v>
+        <v>-17.25796670672525</v>
       </c>
       <c r="F21">
-        <v>-3.658285973534853</v>
+        <v>-3.36785870537854</v>
       </c>
       <c r="G21">
-        <v>-5.374042830022645</v>
+        <v>-4.816374812841334</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.071376842406432</v>
       </c>
       <c r="E22">
-        <v>-19.3588299537857</v>
+        <v>-17.1257488511233</v>
       </c>
       <c r="F22">
-        <v>-3.645462017772113</v>
+        <v>-3.000669943474409</v>
       </c>
       <c r="G22">
-        <v>-5.363247141019081</v>
+        <v>-5.087683951421226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.434621225908442</v>
       </c>
       <c r="E23">
-        <v>-18.6022442159022</v>
+        <v>-18.02765331991295</v>
       </c>
       <c r="F23">
-        <v>-3.045617987117713</v>
+        <v>-2.826018617002967</v>
       </c>
       <c r="G23">
-        <v>-4.830785617573782</v>
+        <v>-4.931303711782673</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.483638749694689</v>
       </c>
       <c r="E24">
-        <v>-20.16212237258433</v>
+        <v>-18.76396507966412</v>
       </c>
       <c r="F24">
-        <v>-3.192904196437673</v>
+        <v>-2.428817275728007</v>
       </c>
       <c r="G24">
-        <v>-5.430394936192119</v>
+        <v>-4.882039483612779</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.243440789693556</v>
       </c>
       <c r="E25">
-        <v>-20.41539992383333</v>
+        <v>-19.18926124456849</v>
       </c>
       <c r="F25">
-        <v>-2.585174936476025</v>
+        <v>-2.556843114565476</v>
       </c>
       <c r="G25">
-        <v>-4.91714450851121</v>
+        <v>-4.858107549909387</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.74992909518007</v>
       </c>
       <c r="E26">
-        <v>-21.16717189384669</v>
+        <v>-18.93603350653357</v>
       </c>
       <c r="F26">
-        <v>-2.542405499102083</v>
+        <v>-2.212958812804303</v>
       </c>
       <c r="G26">
-        <v>-4.947978929663982</v>
+        <v>-5.504481634815469</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.049901751495704</v>
       </c>
       <c r="E27">
-        <v>-20.56832649107236</v>
+        <v>-18.91262129591392</v>
       </c>
       <c r="F27">
-        <v>-2.86486490635725</v>
+        <v>-2.384022480054221</v>
       </c>
       <c r="G27">
-        <v>-5.335081019570962</v>
+        <v>-5.002387745601904</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.196086497550299</v>
       </c>
       <c r="E28">
-        <v>-21.54897659438139</v>
+        <v>-19.0388389234557</v>
       </c>
       <c r="F28">
-        <v>-2.727345148716295</v>
+        <v>-2.316507223256449</v>
       </c>
       <c r="G28">
-        <v>-6.326539750399593</v>
+        <v>-5.785858142380284</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.2369228833079396</v>
       </c>
       <c r="E29">
-        <v>-21.05351625320218</v>
+        <v>-18.45433066938966</v>
       </c>
       <c r="F29">
-        <v>-2.670108274652461</v>
+        <v>-2.309370838081332</v>
       </c>
       <c r="G29">
-        <v>-5.113370474260432</v>
+        <v>-5.393485663974785</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.7776053397035649</v>
       </c>
       <c r="E30">
-        <v>-21.35066566063749</v>
+        <v>-18.34587824537996</v>
       </c>
       <c r="F30">
-        <v>-2.817543590104925</v>
+        <v>-2.276054729508139</v>
       </c>
       <c r="G30">
-        <v>-6.561843395694371</v>
+        <v>-5.891338744352542</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.797264917585288</v>
       </c>
       <c r="E31">
-        <v>-20.2543266318545</v>
+        <v>-18.49991881722488</v>
       </c>
       <c r="F31">
-        <v>-2.618291408505143</v>
+        <v>-2.5375280718344</v>
       </c>
       <c r="G31">
-        <v>-6.423022289596113</v>
+        <v>-5.527119145213005</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.774646007434248</v>
       </c>
       <c r="E32">
-        <v>-19.81266909036042</v>
+        <v>-18.60650550994341</v>
       </c>
       <c r="F32">
-        <v>-3.006137996700288</v>
+        <v>-2.528338992235145</v>
       </c>
       <c r="G32">
-        <v>-5.801851387880503</v>
+        <v>-5.3588904630894</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.667541492840373</v>
       </c>
       <c r="E33">
-        <v>-19.63399361991378</v>
+        <v>-18.20945796589889</v>
       </c>
       <c r="F33">
-        <v>-2.711816573383416</v>
+        <v>-2.375655969285945</v>
       </c>
       <c r="G33">
-        <v>-5.097741388769532</v>
+        <v>-5.681261456067011</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.436646775136767</v>
       </c>
       <c r="E34">
-        <v>-19.39296106238152</v>
+        <v>-17.47742561408497</v>
       </c>
       <c r="F34">
-        <v>-3.264937369050313</v>
+        <v>-2.608654182140973</v>
       </c>
       <c r="G34">
-        <v>-6.672127599244113</v>
+        <v>-4.741086386187229</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.049056964292785</v>
       </c>
       <c r="E35">
-        <v>-19.17483352638005</v>
+        <v>-17.26622211484123</v>
       </c>
       <c r="F35">
-        <v>-2.865506891094419</v>
+        <v>-2.275828585207174</v>
       </c>
       <c r="G35">
-        <v>-5.578008851242681</v>
+        <v>-6.039495588871546</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.479344446863187</v>
       </c>
       <c r="E36">
-        <v>-17.25441185462923</v>
+        <v>-16.76013344516602</v>
       </c>
       <c r="F36">
-        <v>-2.67937273568537</v>
+        <v>-2.708987698702855</v>
       </c>
       <c r="G36">
-        <v>-5.403404058410441</v>
+        <v>-5.884591852543508</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.708796441718923</v>
       </c>
       <c r="E37">
-        <v>-18.78601874808147</v>
+        <v>-16.28109335073862</v>
       </c>
       <c r="F37">
-        <v>-3.258406520446641</v>
+        <v>-2.46718725382568</v>
       </c>
       <c r="G37">
-        <v>-5.755573271787031</v>
+        <v>-5.271773457223479</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.728175510173816</v>
       </c>
       <c r="E38">
-        <v>-16.84432683391663</v>
+        <v>-15.79677305561827</v>
       </c>
       <c r="F38">
-        <v>-3.418896906167226</v>
+        <v>-2.949656593707807</v>
       </c>
       <c r="G38">
-        <v>-4.908388115559838</v>
+        <v>-5.58728168929818</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.540303406118275</v>
       </c>
       <c r="E39">
-        <v>-18.02261312834241</v>
+        <v>-15.16884126429268</v>
       </c>
       <c r="F39">
-        <v>-2.721424806888487</v>
+        <v>-2.69572387984923</v>
       </c>
       <c r="G39">
-        <v>-5.447533630448926</v>
+        <v>-4.823270679199636</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.158872484985837</v>
       </c>
       <c r="E40">
-        <v>-17.24302727097395</v>
+        <v>-14.98237681855284</v>
       </c>
       <c r="F40">
-        <v>-3.085819485542975</v>
+        <v>-3.049247064709378</v>
       </c>
       <c r="G40">
-        <v>-4.159893632403858</v>
+        <v>-4.996620775272493</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.606313870638854</v>
       </c>
       <c r="E41">
-        <v>-16.78552007045302</v>
+        <v>-14.39765572620844</v>
       </c>
       <c r="F41">
-        <v>-2.984110879092447</v>
+        <v>-2.778223474596241</v>
       </c>
       <c r="G41">
-        <v>-4.846457740156692</v>
+        <v>-4.706891761312098</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.914364838565772</v>
       </c>
       <c r="E42">
-        <v>-16.80164143792032</v>
+        <v>-12.93268079930505</v>
       </c>
       <c r="F42">
-        <v>-3.248219258127013</v>
+        <v>-2.799461986436617</v>
       </c>
       <c r="G42">
-        <v>-4.796054684321288</v>
+        <v>-4.729790804807236</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.12217048822489</v>
       </c>
       <c r="E43">
-        <v>-14.95102619299774</v>
+        <v>-13.57707359364853</v>
       </c>
       <c r="F43">
-        <v>-3.023416912355283</v>
+        <v>-3.25186076122972</v>
       </c>
       <c r="G43">
-        <v>-5.228133845924806</v>
+        <v>-4.742046444393618</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.272716080486227</v>
       </c>
       <c r="E44">
-        <v>-15.02459125325234</v>
+        <v>-12.15645506965028</v>
       </c>
       <c r="F44">
-        <v>-3.605703695907348</v>
+        <v>-3.28551318696845</v>
       </c>
       <c r="G44">
-        <v>-3.949147613919394</v>
+        <v>-4.525265301391062</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.415237115940343</v>
       </c>
       <c r="E45">
-        <v>-14.63512437469666</v>
+        <v>-12.21619469875946</v>
       </c>
       <c r="F45">
-        <v>-3.431200647201007</v>
+        <v>-3.229156039086388</v>
       </c>
       <c r="G45">
-        <v>-4.759056027374394</v>
+        <v>-4.35343805626627</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6007324861467803</v>
       </c>
       <c r="E46">
-        <v>-14.18939573506968</v>
+        <v>-11.59348876643872</v>
       </c>
       <c r="F46">
-        <v>-3.878883526369972</v>
+        <v>-3.429299544011582</v>
       </c>
       <c r="G46">
-        <v>-3.906931537202607</v>
+        <v>-3.697112471469139</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.1227378480555364</v>
       </c>
       <c r="E47">
-        <v>-14.4393720287671</v>
+        <v>-11.80479189211063</v>
       </c>
       <c r="F47">
-        <v>-3.386654361748061</v>
+        <v>-3.345202028544571</v>
       </c>
       <c r="G47">
-        <v>-4.135322763411388</v>
+        <v>-4.095960376949453</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.7158510845869273</v>
       </c>
       <c r="E48">
-        <v>-13.66453201215867</v>
+        <v>-11.31474760584459</v>
       </c>
       <c r="F48">
-        <v>-4.041986582878986</v>
+        <v>-3.669724899000111</v>
       </c>
       <c r="G48">
-        <v>-4.657064740400527</v>
+        <v>-4.408515602403124</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.143916868180614</v>
       </c>
       <c r="E49">
-        <v>-11.65159814490515</v>
+        <v>-11.12209726461028</v>
       </c>
       <c r="F49">
-        <v>-3.994160790878357</v>
+        <v>-3.602792812853911</v>
       </c>
       <c r="G49">
-        <v>-4.779243734072869</v>
+        <v>-3.795253593980833</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.384588827318277</v>
       </c>
       <c r="E50">
-        <v>-11.66459939378117</v>
+        <v>-9.689759049880173</v>
       </c>
       <c r="F50">
-        <v>-3.670970763573921</v>
+        <v>-4.048124785333731</v>
       </c>
       <c r="G50">
-        <v>-4.710245343943379</v>
+        <v>-4.301429385844319</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.42955288428427</v>
       </c>
       <c r="E51">
-        <v>-12.03783169301935</v>
+        <v>-9.441897553544344</v>
       </c>
       <c r="F51">
-        <v>-3.703092366352278</v>
+        <v>-3.987642367785727</v>
       </c>
       <c r="G51">
-        <v>-4.816745593941733</v>
+        <v>-4.026670658812507</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.28286486851147</v>
       </c>
       <c r="E52">
-        <v>-11.53178830808421</v>
+        <v>-9.584752794590312</v>
       </c>
       <c r="F52">
-        <v>-4.061504575623748</v>
+        <v>-3.911907221249977</v>
       </c>
       <c r="G52">
-        <v>-4.719554597999809</v>
+        <v>-4.053214612946383</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.9581462625466024</v>
       </c>
       <c r="E53">
-        <v>-11.52511333739691</v>
+        <v>-8.661220333940028</v>
       </c>
       <c r="F53">
-        <v>-4.39493156729198</v>
+        <v>-4.067047181915879</v>
       </c>
       <c r="G53">
-        <v>-4.728079252763433</v>
+        <v>-3.444584057733533</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.4809583419638124</v>
       </c>
       <c r="E54">
-        <v>-10.25474505249915</v>
+        <v>-7.570632467146782</v>
       </c>
       <c r="F54">
-        <v>-4.050474863655473</v>
+        <v>-4.06415038110829</v>
       </c>
       <c r="G54">
-        <v>-4.322120295464764</v>
+        <v>-4.026154213708381</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.1137518426627229</v>
       </c>
       <c r="E55">
-        <v>-11.4909822288011</v>
+        <v>-7.716318004447546</v>
       </c>
       <c r="F55">
-        <v>-4.222360271368967</v>
+        <v>-4.19574482671702</v>
       </c>
       <c r="G55">
-        <v>-4.87998694537843</v>
+        <v>-4.394250461674405</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.7894664306092068</v>
       </c>
       <c r="E56">
-        <v>-9.994194771993827</v>
+        <v>-7.260812389438008</v>
       </c>
       <c r="F56">
-        <v>-4.074279657709722</v>
+        <v>-4.423813425157988</v>
       </c>
       <c r="G56">
-        <v>-4.796783004339928</v>
+        <v>-3.970262273368865</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.507112151319999</v>
       </c>
       <c r="E57">
-        <v>-10.40647610260015</v>
+        <v>-6.99154479646792</v>
       </c>
       <c r="F57">
-        <v>-4.443577443021381</v>
+        <v>-4.520618924951346</v>
       </c>
       <c r="G57">
-        <v>-5.222204658863972</v>
+        <v>-4.133684043369448</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.227807235950682</v>
       </c>
       <c r="E58">
-        <v>-9.63086624541042</v>
+        <v>-6.818611431063005</v>
       </c>
       <c r="F58">
-        <v>-4.158736684629549</v>
+        <v>-4.739903515453029</v>
       </c>
       <c r="G58">
-        <v>-5.112900376793855</v>
+        <v>-4.110583056596414</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.915506723732947</v>
       </c>
       <c r="E59">
-        <v>-9.525198832915439</v>
+        <v>-6.99384073278981</v>
       </c>
       <c r="F59">
-        <v>-4.1348432552632</v>
+        <v>-4.712361127677347</v>
       </c>
       <c r="G59">
-        <v>-5.687329686040495</v>
+        <v>-3.998458189726838</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.542484939722035</v>
       </c>
       <c r="E60">
-        <v>-8.863353299746402</v>
+        <v>-6.504326277982667</v>
       </c>
       <c r="F60">
-        <v>-4.798851796571047</v>
+        <v>-4.792571943290424</v>
       </c>
       <c r="G60">
-        <v>-4.675802428152801</v>
+        <v>-3.93117466218669</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.08367071616239</v>
       </c>
       <c r="E61">
-        <v>-9.234027011170252</v>
+        <v>-5.946241669751379</v>
       </c>
       <c r="F61">
-        <v>-4.939738039336978</v>
+        <v>-4.858481824061569</v>
       </c>
       <c r="G61">
-        <v>-5.57820086288396</v>
+        <v>-4.338696196979895</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.519528627298193</v>
       </c>
       <c r="E62">
-        <v>-7.257040170589618</v>
+        <v>-5.521475336305908</v>
       </c>
       <c r="F62">
-        <v>-4.450043678967634</v>
+        <v>-4.528364160167522</v>
       </c>
       <c r="G62">
-        <v>-4.966915250148613</v>
+        <v>-4.160823895700394</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.836887559591585</v>
       </c>
       <c r="E63">
-        <v>-7.584869989426898</v>
+        <v>-5.588849972592027</v>
       </c>
       <c r="F63">
-        <v>-4.862691587202597</v>
+        <v>-4.653101380415877</v>
       </c>
       <c r="G63">
-        <v>-5.36247909445397</v>
+        <v>-4.074607358221153</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.030988230988981</v>
       </c>
       <c r="E64">
-        <v>-8.473515086322092</v>
+        <v>-5.185317653768521</v>
       </c>
       <c r="F64">
-        <v>-4.491793396068729</v>
+        <v>-4.956995417439501</v>
       </c>
       <c r="G64">
-        <v>-4.91396307424797</v>
+        <v>-4.538696184643885</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.102985876316104</v>
       </c>
       <c r="E65">
-        <v>-7.409378036207649</v>
+        <v>-5.5707677758794</v>
       </c>
       <c r="F65">
-        <v>-4.852083514242346</v>
+        <v>-5.104989052521452</v>
       </c>
       <c r="G65">
-        <v>-5.688564519526643</v>
+        <v>-4.276146749560906</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.061390614202131</v>
       </c>
       <c r="E66">
-        <v>-8.816814172369574</v>
+        <v>-5.653054677072777</v>
       </c>
       <c r="F66">
-        <v>-4.863869525649378</v>
+        <v>-4.828291145699138</v>
       </c>
       <c r="G66">
-        <v>-5.600576840183893</v>
+        <v>-4.667413505756288</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.920287345335791</v>
       </c>
       <c r="E67">
-        <v>-6.898131434637697</v>
+        <v>-4.217922393879942</v>
       </c>
       <c r="F67">
-        <v>-4.442308384160292</v>
+        <v>-5.130111779113555</v>
       </c>
       <c r="G67">
-        <v>-5.418549804252606</v>
+        <v>-4.11986582628853</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.698741558709871</v>
       </c>
       <c r="E68">
-        <v>-7.628139558570188</v>
+        <v>-5.24453197989282</v>
       </c>
       <c r="F68">
-        <v>-4.75944801595468</v>
+        <v>-5.226162636202964</v>
       </c>
       <c r="G68">
-        <v>-5.473915367851378</v>
+        <v>-3.675458193096766</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.418662149977572</v>
       </c>
       <c r="E69">
-        <v>-7.089771926168298</v>
+        <v>-4.714523910509088</v>
       </c>
       <c r="F69">
-        <v>-5.203636013051233</v>
+        <v>-5.34484614747166</v>
       </c>
       <c r="G69">
-        <v>-5.411819465171268</v>
+        <v>-3.828594098106834</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.102926792079404</v>
       </c>
       <c r="E70">
-        <v>-7.986962253515965</v>
+        <v>-4.738828230508255</v>
       </c>
       <c r="F70">
-        <v>-5.189697903131729</v>
+        <v>-5.051894015471615</v>
       </c>
       <c r="G70">
-        <v>-5.657965147107159</v>
+        <v>-3.880943754719329</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.772186667435026</v>
       </c>
       <c r="E71">
-        <v>-7.187781689116308</v>
+        <v>-5.043531132588363</v>
       </c>
       <c r="F71">
-        <v>-4.810063749367938</v>
+        <v>-5.244641856224614</v>
       </c>
       <c r="G71">
-        <v>-4.947757123112851</v>
+        <v>-3.902743697095429</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.445151400812576</v>
       </c>
       <c r="E72">
-        <v>-7.457846293511745</v>
+        <v>-4.79890296669401</v>
       </c>
       <c r="F72">
-        <v>-4.403356063778451</v>
+        <v>-5.452197592670059</v>
       </c>
       <c r="G72">
-        <v>-5.037151784309791</v>
+        <v>-3.579455683003441</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.135854043904009</v>
       </c>
       <c r="E73">
-        <v>-7.762182389197231</v>
+        <v>-4.896477996137284</v>
       </c>
       <c r="F73">
-        <v>-4.791764285072694</v>
+        <v>-5.474896516241571</v>
       </c>
       <c r="G73">
-        <v>-5.266115734896864</v>
+        <v>-3.286018858039061</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.852632710101406</v>
       </c>
       <c r="E74">
-        <v>-7.465875277927345</v>
+        <v>-5.664452846150084</v>
       </c>
       <c r="F74">
-        <v>-5.244254180280104</v>
+        <v>-5.544268972756418</v>
       </c>
       <c r="G74">
-        <v>-4.744347273543411</v>
+        <v>-3.27044274127679</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.597540841649154</v>
       </c>
       <c r="E75">
-        <v>-8.403572805273622</v>
+        <v>-5.01023779168397</v>
       </c>
       <c r="F75">
-        <v>-4.8871930382426</v>
+        <v>-5.672256706693359</v>
       </c>
       <c r="G75">
-        <v>-4.725768491977021</v>
+        <v>-2.505120755144695</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.370644318279587</v>
       </c>
       <c r="E76">
-        <v>-7.829317016360944</v>
+        <v>-6.397440705979624</v>
       </c>
       <c r="F76">
-        <v>-5.523602034423973</v>
+        <v>-5.625056332081843</v>
       </c>
       <c r="G76">
-        <v>-4.845007721210491</v>
+        <v>-2.358456966663903</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.168231919650724</v>
       </c>
       <c r="E77">
-        <v>-7.681960472151351</v>
+        <v>-6.69174623173812</v>
       </c>
       <c r="F77">
-        <v>-5.397742376344825</v>
+        <v>-5.887326563849597</v>
       </c>
       <c r="G77">
-        <v>-4.295331360960982</v>
+        <v>-2.313705012064034</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.984712119213783</v>
       </c>
       <c r="E78">
-        <v>-9.260758593237529</v>
+        <v>-6.511494852336809</v>
       </c>
       <c r="F78">
-        <v>-5.377430807628182</v>
+        <v>-5.806846528830611</v>
       </c>
       <c r="G78">
-        <v>-4.701151275347001</v>
+        <v>-2.614769333950896</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.813035831281802</v>
       </c>
       <c r="E79">
-        <v>-10.57787884379048</v>
+        <v>-8.208526901289252</v>
       </c>
       <c r="F79">
-        <v>-5.931179505786401</v>
+        <v>-6.044247514431519</v>
       </c>
       <c r="G79">
-        <v>-3.526503507102798</v>
+        <v>-1.857902481126099</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.649819318088475</v>
       </c>
       <c r="E80">
-        <v>-10.04139052810177</v>
+        <v>-7.611773653506468</v>
       </c>
       <c r="F80">
-        <v>-5.36550563049748</v>
+        <v>-6.026894045710272</v>
       </c>
       <c r="G80">
-        <v>-3.861146692394487</v>
+        <v>-2.373698718326707</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.491675036430066</v>
       </c>
       <c r="E81">
-        <v>-10.63260092369916</v>
+        <v>-8.78428161509847</v>
       </c>
       <c r="F81">
-        <v>-5.634556049457148</v>
+        <v>-5.852535961299421</v>
       </c>
       <c r="G81">
-        <v>-3.610905865626517</v>
+        <v>-2.353332242169111</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.33573530258471</v>
       </c>
       <c r="E82">
-        <v>-11.72409448529394</v>
+        <v>-9.730184737346645</v>
       </c>
       <c r="F82">
-        <v>-5.611954044871763</v>
+        <v>-6.106438025564095</v>
       </c>
       <c r="G82">
-        <v>-2.872614483822571</v>
+        <v>-1.505011568821947</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.178690811872402</v>
       </c>
       <c r="E83">
-        <v>-12.58776957651084</v>
+        <v>-10.18535524527962</v>
       </c>
       <c r="F83">
-        <v>-5.362390140695551</v>
+        <v>-6.54364951239427</v>
       </c>
       <c r="G83">
-        <v>-3.252923334282967</v>
+        <v>-1.475822488802194</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.020075417170078</v>
       </c>
       <c r="E84">
-        <v>-12.79989235597814</v>
+        <v>-11.77101853296142</v>
       </c>
       <c r="F84">
-        <v>-5.711855982016786</v>
+        <v>-6.565964901858287</v>
       </c>
       <c r="G84">
-        <v>-3.567349017966326</v>
+        <v>-1.32398431764352</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.8595651164048098</v>
       </c>
       <c r="E85">
-        <v>-14.43033319464779</v>
+        <v>-12.81139015148361</v>
       </c>
       <c r="F85">
-        <v>-5.922245563347207</v>
+        <v>-6.630574659990739</v>
       </c>
       <c r="G85">
-        <v>-2.708100233794029</v>
+        <v>-1.499860359962842</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.6976132546900075</v>
       </c>
       <c r="E86">
-        <v>-15.58763454052203</v>
+        <v>-13.60401348552016</v>
       </c>
       <c r="F86">
-        <v>-6.05626132687432</v>
+        <v>-6.695305359763998</v>
       </c>
       <c r="G86">
-        <v>-3.401795256638453</v>
+        <v>-1.078454397177934</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5347130548560259</v>
       </c>
       <c r="E87">
-        <v>-16.70636234479894</v>
+        <v>-15.41580159430098</v>
       </c>
       <c r="F87">
-        <v>-5.973393937000466</v>
+        <v>-6.573906460148925</v>
       </c>
       <c r="G87">
-        <v>-3.4789839364321</v>
+        <v>-1.059776299245366</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3733934040120859</v>
       </c>
       <c r="E88">
-        <v>-17.88479355039297</v>
+        <v>-16.3517511306803</v>
       </c>
       <c r="F88">
-        <v>-5.985378756584169</v>
+        <v>-6.759610692875921</v>
       </c>
       <c r="G88">
-        <v>-2.867526175328711</v>
+        <v>-0.9600759097846745</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.217300789430784</v>
       </c>
       <c r="E89">
-        <v>-19.49713407845396</v>
+        <v>-18.02403959765483</v>
       </c>
       <c r="F89">
-        <v>-6.511950791175043</v>
+        <v>-6.733477358052403</v>
       </c>
       <c r="G89">
-        <v>-3.393697662249395</v>
+        <v>-0.978710970625232</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.07182472481611868</v>
       </c>
       <c r="E90">
-        <v>-20.51387159113012</v>
+        <v>-19.06559767636703</v>
       </c>
       <c r="F90">
-        <v>-6.423605821850177</v>
+        <v>-6.566725343134056</v>
       </c>
       <c r="G90">
-        <v>-3.735683637547187</v>
+        <v>-1.014961444280251</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.05395782184621982</v>
       </c>
       <c r="E91">
-        <v>-23.59277654047119</v>
+        <v>-21.58252352983021</v>
       </c>
       <c r="F91">
-        <v>-6.087308537131245</v>
+        <v>-6.74463795207032</v>
       </c>
       <c r="G91">
-        <v>-3.346012564301733</v>
+        <v>-1.675736402282163</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.1467063605705504</v>
       </c>
       <c r="E92">
-        <v>-24.73986164898413</v>
+        <v>-23.79533518283429</v>
       </c>
       <c r="F92">
-        <v>-6.230925907224207</v>
+        <v>-6.986353075105008</v>
       </c>
       <c r="G92">
-        <v>-3.344638687902936</v>
+        <v>-2.095685725029791</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.1893479766281936</v>
       </c>
       <c r="E93">
-        <v>-26.71879573338806</v>
+        <v>-26.12006807093793</v>
       </c>
       <c r="F93">
-        <v>-6.291166441490593</v>
+        <v>-6.755024436750322</v>
       </c>
       <c r="G93">
-        <v>-4.319779739768499</v>
+        <v>-2.08756164627642</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1628011448844242</v>
       </c>
       <c r="E94">
-        <v>-28.94048772392118</v>
+        <v>-27.24288055876976</v>
       </c>
       <c r="F94">
-        <v>-6.432107770688811</v>
+        <v>-6.644937308204177</v>
       </c>
       <c r="G94">
-        <v>-3.74530408288431</v>
+        <v>-2.547644712596633</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.049099123590162</v>
       </c>
       <c r="E95">
-        <v>-30.44377354092945</v>
+        <v>-30.78775642655209</v>
       </c>
       <c r="F95">
-        <v>-6.079865656017092</v>
+        <v>-6.778640777220435</v>
       </c>
       <c r="G95">
-        <v>-5.220125636265309</v>
+        <v>-3.437539216825964</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1717263683546699</v>
       </c>
       <c r="E96">
-        <v>-33.15290141670019</v>
+        <v>-32.32523675079229</v>
       </c>
       <c r="F96">
-        <v>-6.478706336382192</v>
+        <v>-6.887266665668041</v>
       </c>
       <c r="G96">
-        <v>-5.284297250998542</v>
+        <v>-3.567805873250746</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.4968732280808335</v>
       </c>
       <c r="E97">
-        <v>-36.04808617555007</v>
+        <v>-34.39093639718318</v>
       </c>
       <c r="F97">
-        <v>-6.275381072262845</v>
+        <v>-6.755439863002826</v>
       </c>
       <c r="G97">
-        <v>-5.616676023141369</v>
+        <v>-3.912738234078489</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.9347632783813953</v>
       </c>
       <c r="E98">
-        <v>-38.68655400714212</v>
+        <v>-36.94636107242258</v>
       </c>
       <c r="F98">
-        <v>-6.132848863467551</v>
+        <v>-6.650606654708938</v>
       </c>
       <c r="G98">
-        <v>-7.01990702923563</v>
+        <v>-4.594939042810563</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.445933345044708</v>
       </c>
       <c r="E99">
-        <v>-40.89435490365671</v>
+        <v>-39.97571772340872</v>
       </c>
       <c r="F99">
-        <v>-6.866904980723527</v>
+        <v>-6.767741118934398</v>
       </c>
       <c r="G99">
-        <v>-5.922673057881744</v>
+        <v>-5.404509780620558</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.042619000185974</v>
       </c>
       <c r="E100">
-        <v>-42.81000582804045</v>
+        <v>-42.33373489546874</v>
       </c>
       <c r="F100">
-        <v>-6.27482316681706</v>
+        <v>-6.545780487537972</v>
       </c>
       <c r="G100">
-        <v>-7.045275739703064</v>
+        <v>-5.868532396132503</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.636959649507172</v>
       </c>
       <c r="E101">
-        <v>-45.97230489046977</v>
+        <v>-45.4586853685198</v>
       </c>
       <c r="F101">
-        <v>-6.450307002528316</v>
+        <v>-6.504183604222694</v>
       </c>
       <c r="G101">
-        <v>-6.887418996753996</v>
+        <v>-6.157625785349359</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.3013450648456</v>
       </c>
       <c r="E102">
-        <v>-48.37957827431123</v>
+        <v>-47.50450727825403</v>
       </c>
       <c r="F102">
-        <v>-6.281708142485428</v>
+        <v>-6.564395145629981</v>
       </c>
       <c r="G102">
-        <v>-7.721626814467246</v>
+        <v>-7.049188804530483</v>
       </c>
     </row>
   </sheetData>
